--- a/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
@@ -499,10 +499,9 @@
           <t>+60 14-937 2872</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Produttore/system integrator di macchinari custom (laser, ultrasonica, robot) per medicale/farma/automotive; offre anche 'Air Purifying System'. Fit di nicchia più ampio del solo dust collection. Fonte: WebFetch sito ufficiale.</t>
+          <t>Produttore/system integrator di macchinari custom (laser, ultrasonica, robot) per medicale/farma/automotive; offre anche 'Air Purifying System'. Fit di nicchia più ampio del solo dust collection. Fonte: WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -537,10 +536,9 @@
           <t>+607-234 2307 (WhatsApp +60 19-727 3978)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EPC/installatore M&amp;E, dust collector system tra i servizi offerti. Profilo installatore/contractor. Fonte: WebFetch sito ufficiale. Email generica non trovata sul sito.</t>
+          <t>EPC/installatore M&amp;E, dust collector system tra i servizi offerti. Profilo installatore/contractor. Fonte: WebFetch sito ufficiale. Email generica non trovata sul sito. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -582,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore/EPC ambientale, air pollution control e dust collector, ISO 9001/45001. Fonte: WebFetch sito ufficiale.</t>
+          <t>Fornitore/EPC ambientale, air pollution control e dust collector, ISO 9001/45001. Fonte: WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -708,7 +706,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Produttore/distributore fan, blower e dust collector industriali dal 2016. Fonte: WebFetch sito ufficiale.</t>
+          <t>Produttore/distributore fan, blower e dust collector industriali dal 2016. Fonte: WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -750,7 +748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Contractor HVAC/mechanical ventilation con oltre 35 anni di attività. Profilo installatore/contractor. Fonte: WebFetch sito ufficiale.</t>
+          <t>Contractor HVAC/mechanical ventilation con oltre 35 anni di attività. Profilo installatore/contractor. Fonte: WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -792,7 +790,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Produttore filtri (in-line filter, HEPA, air filtration equipment); nessuna conferma esplicita su sacche filtro per dust collector industriali, fit adiacente. Fonte: WebFetch sito ufficiale.</t>
+          <t>Produttore filtri (in-line filter, HEPA, air filtration equipment); nessuna conferma esplicita su sacche filtro per dust collector industriali, fit adiacente. Fonte: WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -834,7 +832,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Distributore hardware industriale generico; confermato prodotto 'Portable Air Dust Collection System TX-DCS2' come linea secondaria. Fonte: WebFetch + WebSearch.</t>
+          <t>Distributore hardware industriale generico; confermato prodotto 'Portable Air Dust Collection System TX-DCS2' come linea secondaria. Fonte: WebFetch + WebSearch. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -918,7 +916,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EPC ambientale (air pollution control, dust collector, waste-to-energy); distributore Donaldson. Fit forte col settore. Sede JB a Taman Ekoflora. Fonte: WebFetch + WebSearch.</t>
+          <t>EPC ambientale (air pollution control, dust collector, waste-to-energy); distributore Donaldson. Fit forte col settore. Sede JB a Taman Ekoflora. Fonte: WebFetch + WebSearch. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -960,7 +958,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Distributore attrezzature industriali (abrasivi, utensili da taglio) con linea di dust collector per macchine da falegnameria. Fit di nicchia (legno). Fonte: WebFetch + WebSearch.</t>
+          <t>Distributore attrezzature industriali (abrasivi, utensili da taglio) con linea di dust collector per macchine da falegnameria. Fit di nicchia (legno). Fonte: WebFetch + WebSearch. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -975,7 +973,6 @@
           <t>KIJ Filtration Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Johor</t>
@@ -986,8 +983,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Nessun sito ufficiale individuato. Esistenza confermata da directory aziendali (CTOS, EMIS), indirizzo Taman Desa Idaman, Senai, Johor. Telefono/email non reperiti da fonte verificabile.</t>
@@ -1146,8 +1141,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Gruppo leader malese (dal 1983) in air pollution control/dust collector/industrial vacuum, con filiale confermata in Johor (Jaya Jaya Cleantech, Skudai). Telefono/email specifici della filiale non reperiti. Fonte: WebSearch (sito HQ bloccato da anti-bot).</t>

--- a/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gruppo leader malese (dal 1983) in air pollution control/dust collector/industrial vacuum, con filiale confermata in Johor (Jaya Jaya Cleantech, Skudai). Telefono/email specifici della filiale non reperiti. Fonte: WebSearch (sito HQ bloccato da anti-bot).</t>
+          <t>Gruppo leader malese (dal 1983) in air pollution control/dust collector/industrial vacuum, con filiale confermata in Johor (Jaya Jaya Cleantech, Skudai). Telefono/email specifici della filiale non reperiti. Fonte: WebSearch (sito HQ bloccato da anti-bot). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
